--- a/assets/species.xlsx
+++ b/assets/species.xlsx
@@ -6822,7 +6822,7 @@
     <xdr:ext cx="1504950" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image64.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6850,7 +6850,7 @@
     <xdr:ext cx="1447800" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image69.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6878,7 +6878,7 @@
     <xdr:ext cx="952500" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image70.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6906,7 +6906,7 @@
     <xdr:ext cx="1371600" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image54.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6934,7 +6934,7 @@
     <xdr:ext cx="1076325" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image76.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image79.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6990,7 +6990,7 @@
     <xdr:ext cx="1028700" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image46.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image62.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7018,7 +7018,7 @@
     <xdr:ext cx="809625" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image9.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7046,7 +7046,7 @@
     <xdr:ext cx="1257300" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image24.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7074,7 +7074,7 @@
     <xdr:ext cx="1162050" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image64.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7102,7 +7102,7 @@
     <xdr:ext cx="1181100" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image43.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7130,7 +7130,7 @@
     <xdr:ext cx="1028700" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image63.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image73.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7158,7 +7158,7 @@
     <xdr:ext cx="1304925" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image71.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7186,7 +7186,7 @@
     <xdr:ext cx="1266825" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image59.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image8.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7214,7 +7214,7 @@
     <xdr:ext cx="1238250" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image67.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image21.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7242,7 +7242,7 @@
     <xdr:ext cx="1685925" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image53.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image27.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7270,7 +7270,7 @@
     <xdr:ext cx="1457325" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image11.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7298,7 +7298,7 @@
     <xdr:ext cx="1247775" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image33.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image63.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7326,7 +7326,7 @@
     <xdr:ext cx="1790700" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image47.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image13.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7354,7 +7354,7 @@
     <xdr:ext cx="1714500" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image30.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7382,7 +7382,7 @@
     <xdr:ext cx="2314575" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image33.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7410,7 +7410,7 @@
     <xdr:ext cx="1895475" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image30.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7438,7 +7438,7 @@
     <xdr:ext cx="1943100" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image79.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7466,7 +7466,7 @@
     <xdr:ext cx="1562100" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image29.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image65.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7494,7 +7494,7 @@
     <xdr:ext cx="1609725" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image43.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7522,7 +7522,7 @@
     <xdr:ext cx="1876425" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image10.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7550,7 +7550,7 @@
     <xdr:ext cx="2105025" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image71.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image81.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7578,7 +7578,7 @@
     <xdr:ext cx="1809750" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image16.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image83.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7606,7 +7606,7 @@
     <xdr:ext cx="1704975" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image42.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image74.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7634,7 +7634,7 @@
     <xdr:ext cx="1981200" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image80.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7662,7 +7662,7 @@
     <xdr:ext cx="1562100" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image78.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image48.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7690,7 +7690,7 @@
     <xdr:ext cx="2000250" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image32.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image31.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7718,7 +7718,7 @@
     <xdr:ext cx="3619500" cy="2152650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image81.jpg" title="Image"/>
+        <xdr:cNvPr id="0" name="image19.jpg" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7746,7 +7746,7 @@
     <xdr:ext cx="5629275" cy="4876800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image69.jpg" title="Image"/>
+        <xdr:cNvPr id="0" name="image49.jpg" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7774,7 +7774,7 @@
     <xdr:ext cx="1714500" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image28.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7802,7 +7802,7 @@
     <xdr:ext cx="2600325" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image40.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image12.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7830,7 +7830,7 @@
     <xdr:ext cx="4419600" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image72.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7858,7 +7858,7 @@
     <xdr:ext cx="2933700" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image56.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7886,7 +7886,7 @@
     <xdr:ext cx="7143750" cy="3143250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image14.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7923,7 +7923,7 @@
     <xdr:ext cx="1971675" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image68.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image66.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7951,7 +7951,7 @@
     <xdr:ext cx="1381125" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image36.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -7979,7 +7979,7 @@
     <xdr:ext cx="1504950" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image66.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image72.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8007,7 +8007,7 @@
     <xdr:ext cx="1009650" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image18.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8035,7 +8035,7 @@
     <xdr:ext cx="2390775" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image28.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image61.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8063,7 +8063,7 @@
     <xdr:ext cx="1562100" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image65.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image67.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8091,7 +8091,7 @@
     <xdr:ext cx="2590800" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image83.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image77.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8119,7 +8119,7 @@
     <xdr:ext cx="1343025" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image54.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image44.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8147,7 +8147,7 @@
     <xdr:ext cx="2733675" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image44.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image37.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8175,7 +8175,7 @@
     <xdr:ext cx="1066800" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image80.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image76.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8203,7 +8203,7 @@
     <xdr:ext cx="1657350" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image32.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8231,7 +8231,7 @@
     <xdr:ext cx="1057275" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image20.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8259,7 +8259,7 @@
     <xdr:ext cx="1962150" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image25.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8287,7 +8287,7 @@
     <xdr:ext cx="1143000" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image52.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8315,7 +8315,7 @@
     <xdr:ext cx="1847850" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image48.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image58.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8343,7 +8343,7 @@
     <xdr:ext cx="1685925" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image77.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image60.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8371,7 +8371,7 @@
     <xdr:ext cx="2305050" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image35.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image46.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8399,7 +8399,7 @@
     <xdr:ext cx="2438400" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image24.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8427,7 +8427,7 @@
     <xdr:ext cx="1695450" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image22.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8455,7 +8455,7 @@
     <xdr:ext cx="1447800" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image23.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8483,7 +8483,7 @@
     <xdr:ext cx="1619250" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image29.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8511,7 +8511,7 @@
     <xdr:ext cx="1247775" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image17.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8539,7 +8539,7 @@
     <xdr:ext cx="2124075" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image31.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image59.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8567,7 +8567,7 @@
     <xdr:ext cx="2133600" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image62.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image75.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8595,7 +8595,7 @@
     <xdr:ext cx="1743075" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image38.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image15.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8623,7 +8623,7 @@
     <xdr:ext cx="2552700" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image37.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image45.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8651,7 +8651,7 @@
     <xdr:ext cx="1847850" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image75.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image41.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8679,7 +8679,7 @@
     <xdr:ext cx="1866900" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image34.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image16.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8707,7 +8707,7 @@
     <xdr:ext cx="1962150" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image60.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image34.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8735,7 +8735,7 @@
     <xdr:ext cx="1657350" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image36.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image51.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8763,7 +8763,7 @@
     <xdr:ext cx="2009775" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image74.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image39.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8791,7 +8791,7 @@
     <xdr:ext cx="1628775" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image41.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image26.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8819,7 +8819,7 @@
     <xdr:ext cx="2247900" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image56.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image70.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8847,7 +8847,7 @@
     <xdr:ext cx="1885950" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image39.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image35.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8875,7 +8875,7 @@
     <xdr:ext cx="1028700" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image45.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image38.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8903,7 +8903,7 @@
     <xdr:ext cx="942975" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image51.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image40.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8931,7 +8931,7 @@
     <xdr:ext cx="1981200" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image73.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image82.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8959,7 +8959,7 @@
     <xdr:ext cx="1971675" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image61.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image55.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -8987,7 +8987,7 @@
     <xdr:ext cx="1590675" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image55.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image42.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9015,7 +9015,7 @@
     <xdr:ext cx="1990725" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image50.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image47.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9043,7 +9043,7 @@
     <xdr:ext cx="2324100" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image49.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image53.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9071,7 +9071,7 @@
     <xdr:ext cx="2219325" cy="971550"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image82.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image78.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9099,7 +9099,7 @@
     <xdr:ext cx="1609725" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image52.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image68.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9127,7 +9127,7 @@
     <xdr:ext cx="1323975" cy="981075"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image58.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image50.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
